--- a/dataset/DevelopmentBenchmark/Task06/test6_output.xlsx
+++ b/dataset/DevelopmentBenchmark/Task06/test6_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,69 +413,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Correlation Coefficient</t>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Fare</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Pclass</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SibSp</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Parch</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>HasCabin</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Embarked_C</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Embarked_Q</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Embarked_S</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.543</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5433513806577549</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>-0.06980851528714313</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Fare</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.2573065223849626</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cabin</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.01882524916705811</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Embarked</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.1697176771641296</v>
+        <v>-0.077</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.338</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.156</v>
       </c>
     </row>
   </sheetData>
